--- a/PMSM_Control_01/Motor_Para.xlsx
+++ b/PMSM_Control_01/Motor_Para.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\STM32\Motor\PMSM_Control\Project\PMSM_Control_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA187FC9-EF27-4EEC-973E-26F1E2CB2EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22E0138-C55D-4155-86B3-F400C7949682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -499,22 +499,22 @@
         <v>209.43950666666669</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E7">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G7">
         <f>C7*E7</f>
-        <v>20.943950666666669</v>
+        <v>104.71975333333334</v>
       </c>
       <c r="I7">
         <f>2*D7*G7</f>
-        <v>209.43950666666669</v>
+        <v>148.07373121333333</v>
       </c>
       <c r="J7">
         <f>G7*G7*$K$3</f>
-        <v>2.193245347638836E-2</v>
+        <v>0.54831133690970901</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -530,22 +530,22 @@
         <v>209.43950666666669</v>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E8">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G8">
         <f t="shared" ref="G8:G16" si="1">C8*E8</f>
-        <v>20.943950666666669</v>
+        <v>104.71975333333334</v>
       </c>
       <c r="I8">
         <f>2*D8*G8</f>
-        <v>209.43950666666669</v>
+        <v>148.07373121333333</v>
       </c>
       <c r="J8">
         <f t="shared" ref="J8:J16" si="2">G8*G8*$K$3</f>
-        <v>2.193245347638836E-2</v>
+        <v>0.54831133690970901</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -561,22 +561,22 @@
         <v>418.87901333333338</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E9">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>41.887901333333339</v>
+        <v>209.43950666666669</v>
       </c>
       <c r="I9">
-        <f t="shared" ref="I8:I16" si="4">2*D9*G9</f>
-        <v>418.87901333333338</v>
+        <f t="shared" ref="I9:I16" si="4">2*D9*G9</f>
+        <v>296.14746242666666</v>
       </c>
       <c r="J9">
         <f t="shared" si="2"/>
-        <v>8.7729813905553441E-2</v>
+        <v>2.1932453476388361</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -592,22 +592,22 @@
         <v>628.31852000000003</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E10">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
         <f t="shared" si="1"/>
-        <v>62.831852000000005</v>
+        <v>314.15926000000002</v>
       </c>
       <c r="I10">
         <f t="shared" si="4"/>
-        <v>628.31852000000003</v>
+        <v>444.22119364000002</v>
       </c>
       <c r="J10">
         <f t="shared" si="2"/>
-        <v>0.19739208128749525</v>
+        <v>4.9348020321873802</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -623,22 +623,22 @@
         <v>837.75802666666675</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E11">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>83.775802666666678</v>
+        <v>418.87901333333338</v>
       </c>
       <c r="I11">
         <f t="shared" si="4"/>
-        <v>837.75802666666675</v>
+        <v>592.29492485333333</v>
       </c>
       <c r="J11">
         <f t="shared" si="2"/>
-        <v>0.35091925562221377</v>
+        <v>8.7729813905553442</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -654,22 +654,22 @@
         <v>1047.1975333333332</v>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E12">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>104.71975333333333</v>
+        <v>523.59876666666662</v>
       </c>
       <c r="I12">
         <f t="shared" si="4"/>
-        <v>1047.1975333333332</v>
+        <v>740.36865606666652</v>
       </c>
       <c r="J12">
         <f t="shared" si="2"/>
-        <v>0.5483113369097089</v>
+        <v>13.70778342274272</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -685,22 +685,22 @@
         <v>1256.6370400000001</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E13">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>125.66370400000001</v>
+        <v>628.31852000000003</v>
       </c>
       <c r="I13">
         <f t="shared" si="4"/>
-        <v>1256.6370400000001</v>
+        <v>888.44238728000005</v>
       </c>
       <c r="J13">
         <f t="shared" si="2"/>
-        <v>0.78956832514998099</v>
+        <v>19.739208128749521</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -716,22 +716,22 @@
         <v>1466.0765466666667</v>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E14">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G14">
         <f t="shared" si="1"/>
-        <v>146.60765466666666</v>
+        <v>733.03827333333334</v>
       </c>
       <c r="I14">
         <f t="shared" si="4"/>
-        <v>1466.0765466666667</v>
+        <v>1036.5161184933334</v>
       </c>
       <c r="J14">
         <f t="shared" si="2"/>
-        <v>1.0746902203430295</v>
+        <v>26.867255508575735</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -747,22 +747,22 @@
         <v>1675.5160533333335</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E15">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G15">
         <f t="shared" si="1"/>
-        <v>167.55160533333336</v>
+        <v>837.75802666666675</v>
       </c>
       <c r="I15">
         <f t="shared" si="4"/>
-        <v>1675.5160533333335</v>
+        <v>1184.5898497066667</v>
       </c>
       <c r="J15">
         <f t="shared" si="2"/>
-        <v>1.4036770224888551</v>
+        <v>35.091925562221377</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -778,22 +778,22 @@
         <v>2094.3950666666665</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="E16">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="G16">
         <f t="shared" si="1"/>
-        <v>209.43950666666666</v>
+        <v>1047.1975333333332</v>
       </c>
       <c r="I16">
         <f t="shared" si="4"/>
-        <v>2094.3950666666665</v>
+        <v>1480.737312133333</v>
       </c>
       <c r="J16">
         <f t="shared" si="2"/>
-        <v>2.1932453476388356</v>
+        <v>54.83113369097088</v>
       </c>
     </row>
   </sheetData>

--- a/PMSM_Control_01/Motor_Para.xlsx
+++ b/PMSM_Control_01/Motor_Para.xlsx
@@ -8,12 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\STM32\Motor\PMSM_Control\Project\PMSM_Control_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22E0138-C55D-4155-86B3-F400C7949682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B3FFCC-5D52-4103-904C-646A53E87A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="磁链观测器" sheetId="1" r:id="rId1"/>
+    <sheet name="滑模观测器" sheetId="2" r:id="rId2"/>
+    <sheet name="DQ轴电流环" sheetId="3" r:id="rId3"/>
+    <sheet name="速度环" sheetId="4" r:id="rId4"/>
+    <sheet name="IF启动参数" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="53">
   <si>
     <t>最大转速</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,13 +94,158 @@
   <si>
     <t>开关频率</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变量名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>增益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>变量类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反电动势系数(V/1000rpm)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反电动势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMO_Lookup_Speed_index</t>
+  </si>
+  <si>
+    <t>NonFlux_Lookup_Speed_index</t>
+  </si>
+  <si>
+    <t>NonFlux_Gama_Lookup_1D</t>
+  </si>
+  <si>
+    <t>NonFlux_PLL_Kp_Lookup_1D</t>
+  </si>
+  <si>
+    <t>NonFlux_PLL_Ki_Lookup_1D</t>
+  </si>
+  <si>
+    <t>SMO_Gain_Lookup_1D</t>
+  </si>
+  <si>
+    <t>SMO_PLL_Ki_Lookup_1D</t>
+  </si>
+  <si>
+    <t>Ld</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rs</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id_Kp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iq_Ki</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Iq_Kp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id_Ki</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带宽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Current_ID_PI_Kp_Lookup_1D</t>
+  </si>
+  <si>
+    <t>Current_IQ_PI_Ki_Lookup_1D</t>
+  </si>
+  <si>
+    <t>惯量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed_Kp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed_Ki</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed_Loop_Speed_PI_Kp_1D</t>
+  </si>
+  <si>
+    <t>Speed_Loop_Speed_Index</t>
+  </si>
+  <si>
+    <t>Current_Lookup_Speed_index</t>
+  </si>
+  <si>
+    <t>Current_ID_PI_Ki_Lookup_1D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Current_IQ_PI_Kp_Lookup_1D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Speed_Loop_Speed_PI_Ki_1D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMO_PLL_Kp_Lookup_1D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF转速</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF_Iq</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IF_Start_Ramp_Sec</t>
+  </si>
+  <si>
+    <t>IF_Start_Iq_A</t>
+  </si>
+  <si>
+    <t>IF_Start_Speed_RPM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="177" formatCode="0.00000"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,13 +260,40 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF9CDCFE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -132,8 +308,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -414,8 +606,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K16"/>
+  <dimension ref="A2:K19"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="9" max="9" width="17.77734375" customWidth="1"/>
+    <col min="10" max="10" width="19.44140625" customWidth="1"/>
+    <col min="11" max="11" width="10.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -485,6 +682,9 @@
       <c r="J6" t="s">
         <v>11</v>
       </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -516,6 +716,9 @@
         <f>G7*G7*$K$3</f>
         <v>0.54831133690970901</v>
       </c>
+      <c r="K7" s="4">
+        <v>100000</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -547,6 +750,9 @@
         <f t="shared" ref="J8:J16" si="2">G8*G8*$K$3</f>
         <v>0.54831133690970901</v>
       </c>
+      <c r="K8" s="4">
+        <v>100000</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -578,6 +784,9 @@
         <f t="shared" si="2"/>
         <v>2.1932453476388361</v>
       </c>
+      <c r="K9" s="4">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -609,6 +818,9 @@
         <f t="shared" si="2"/>
         <v>4.9348020321873802</v>
       </c>
+      <c r="K10" s="4">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -640,6 +852,9 @@
         <f t="shared" si="2"/>
         <v>8.7729813905553442</v>
       </c>
+      <c r="K11" s="4">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -671,6 +886,9 @@
         <f t="shared" si="2"/>
         <v>13.70778342274272</v>
       </c>
+      <c r="K12" s="4">
+        <v>2000000</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -702,6 +920,9 @@
         <f t="shared" si="2"/>
         <v>19.739208128749521</v>
       </c>
+      <c r="K13" s="4">
+        <v>3000000</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -733,6 +954,9 @@
         <f t="shared" si="2"/>
         <v>26.867255508575735</v>
       </c>
+      <c r="K14" s="4">
+        <v>4000000</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -764,6 +988,9 @@
         <f t="shared" si="2"/>
         <v>35.091925562221377</v>
       </c>
+      <c r="K15" s="4">
+        <v>5000000</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -794,6 +1021,43 @@
       <c r="J16">
         <f t="shared" si="2"/>
         <v>54.83113369097088</v>
+      </c>
+      <c r="K16" s="4">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -801,4 +1065,1545 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A66DE823-BC6C-4599-A37B-5D0857471AA8}">
+  <dimension ref="A2:K19"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" customWidth="1"/>
+    <col min="10" max="10" width="25.33203125" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>5000</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <f>A3/60*2*3.1415926</f>
+        <v>523.59876666666662</v>
+      </c>
+      <c r="G3">
+        <f>A3/60*2*3.1415926*C3</f>
+        <v>2094.3950666666665</v>
+      </c>
+      <c r="I3">
+        <v>20000</v>
+      </c>
+      <c r="J3">
+        <v>4.3</v>
+      </c>
+      <c r="K3">
+        <f>1/I3</f>
+        <v>5.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>0.1</v>
+      </c>
+      <c r="B7">
+        <f>$A$3*A7</f>
+        <v>500</v>
+      </c>
+      <c r="C7">
+        <f>B7/60*2*3.1415926*$C$3</f>
+        <v>209.43950666666669</v>
+      </c>
+      <c r="D7">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E7">
+        <v>0.5</v>
+      </c>
+      <c r="G7">
+        <f>C7*E7</f>
+        <v>104.71975333333334</v>
+      </c>
+      <c r="H7">
+        <f>$J$3*B7/1000</f>
+        <v>2.15</v>
+      </c>
+      <c r="I7">
+        <f>2*D7*G7/H7</f>
+        <v>68.871502889922482</v>
+      </c>
+      <c r="J7">
+        <f>G7*G7*$K$3/H7</f>
+        <v>0.25502852879521348</v>
+      </c>
+      <c r="K7" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>0.1</v>
+      </c>
+      <c r="B8">
+        <f>$A$3*A8</f>
+        <v>500</v>
+      </c>
+      <c r="C8">
+        <f t="shared" ref="C8:C16" si="0">B8/60*2*3.1415926*$C$3</f>
+        <v>209.43950666666669</v>
+      </c>
+      <c r="D8">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E8">
+        <v>0.5</v>
+      </c>
+      <c r="G8">
+        <f t="shared" ref="G8:G16" si="1">C8*E8</f>
+        <v>104.71975333333334</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ref="H8:H16" si="2">$J$3*B8/1000</f>
+        <v>2.15</v>
+      </c>
+      <c r="I8">
+        <f t="shared" ref="I8:I16" si="3">2*D8*G8/H8</f>
+        <v>68.871502889922482</v>
+      </c>
+      <c r="J8">
+        <f t="shared" ref="J8:J16" si="4">G8*G8*$K$3/H8</f>
+        <v>0.25502852879521348</v>
+      </c>
+      <c r="K8" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>0.2</v>
+      </c>
+      <c r="B9">
+        <f t="shared" ref="B9:B16" si="5">$A$3*A9</f>
+        <v>1000</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>418.87901333333338</v>
+      </c>
+      <c r="D9">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E9">
+        <v>0.5</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>209.43950666666669</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="2"/>
+        <v>4.3</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>68.871502889922482</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="4"/>
+        <v>0.51005705759042697</v>
+      </c>
+      <c r="K9" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0.3</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="5"/>
+        <v>1500</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>628.31852000000003</v>
+      </c>
+      <c r="D10">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E10">
+        <v>0.5</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>314.15926000000002</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="2"/>
+        <v>6.45</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="3"/>
+        <v>68.871502889922482</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="4"/>
+        <v>0.76508558638564028</v>
+      </c>
+      <c r="K10" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0.4</v>
+      </c>
+      <c r="B11">
+        <f t="shared" si="5"/>
+        <v>2000</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>837.75802666666675</v>
+      </c>
+      <c r="D11">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E11">
+        <v>0.5</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>418.87901333333338</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="2"/>
+        <v>8.6</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="3"/>
+        <v>68.871502889922482</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="4"/>
+        <v>1.0201141151808539</v>
+      </c>
+      <c r="K11" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0.5</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="5"/>
+        <v>2500</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>1047.1975333333332</v>
+      </c>
+      <c r="D12">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E12">
+        <v>0.5</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>523.59876666666662</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>10.75</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="3"/>
+        <v>68.871502889922468</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="4"/>
+        <v>1.2751426439760669</v>
+      </c>
+      <c r="K12" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.6</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="5"/>
+        <v>3000</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>1256.6370400000001</v>
+      </c>
+      <c r="D13">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E13">
+        <v>0.5</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>628.31852000000003</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="2"/>
+        <v>12.9</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="3"/>
+        <v>68.871502889922482</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="4"/>
+        <v>1.5301711727712806</v>
+      </c>
+      <c r="K13" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0.7</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="5"/>
+        <v>3500</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>1466.0765466666667</v>
+      </c>
+      <c r="D14">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E14">
+        <v>0.5</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>733.03827333333334</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="2"/>
+        <v>15.05</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="3"/>
+        <v>68.871502889922482</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="4"/>
+        <v>1.785199701566494</v>
+      </c>
+      <c r="K14" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>0.8</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="5"/>
+        <v>4000</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>1675.5160533333335</v>
+      </c>
+      <c r="D15">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E15">
+        <v>0.5</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>837.75802666666675</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="2"/>
+        <v>17.2</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="3"/>
+        <v>68.871502889922482</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="4"/>
+        <v>2.0402282303617079</v>
+      </c>
+      <c r="K15" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="5"/>
+        <v>5000</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>2094.3950666666665</v>
+      </c>
+      <c r="D16">
+        <v>0.70699999999999996</v>
+      </c>
+      <c r="E16">
+        <v>0.5</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>1047.1975333333332</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="2"/>
+        <v>21.5</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="3"/>
+        <v>68.871502889922468</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="4"/>
+        <v>2.5502852879521338</v>
+      </c>
+      <c r="K16" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3ACED9-E871-45D1-8053-80BA01B87099}">
+  <dimension ref="A2:L22"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" customWidth="1"/>
+    <col min="10" max="10" width="25.33203125" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>5000</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <f>A3/60*2*3.1415926</f>
+        <v>523.59876666666662</v>
+      </c>
+      <c r="G3">
+        <f>A3/60*2*3.1415926*C3</f>
+        <v>2094.3950666666665</v>
+      </c>
+      <c r="I3">
+        <v>20000</v>
+      </c>
+      <c r="J3">
+        <v>4.3</v>
+      </c>
+      <c r="K3">
+        <f>1/I3</f>
+        <v>5.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5.9000000000000003E-4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0.1</v>
+      </c>
+      <c r="B10">
+        <f>$A$3*A10</f>
+        <v>500</v>
+      </c>
+      <c r="C10">
+        <f>B10/60*2*3.1415926*$C$3</f>
+        <v>209.43950666666669</v>
+      </c>
+      <c r="E10">
+        <v>20</v>
+      </c>
+      <c r="F10">
+        <f>$I$3/E10</f>
+        <v>1000</v>
+      </c>
+      <c r="I10" s="5">
+        <f>$A$6*F10*3.1415926*2</f>
+        <v>3.1415926000000001</v>
+      </c>
+      <c r="J10" s="5">
+        <f>$E$6*F10*$K$3*3.1415926*2</f>
+        <v>0.32044244520000004</v>
+      </c>
+      <c r="K10" s="5">
+        <f>$C$6*F10*3.1415926*2</f>
+        <v>3.7070792680000006</v>
+      </c>
+      <c r="L10" s="5">
+        <f>$E$6*F10*$K$3*3.1415926*2</f>
+        <v>0.32044244520000004</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0.1</v>
+      </c>
+      <c r="B11">
+        <f>$A$3*A11</f>
+        <v>500</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ref="C11:C19" si="0">B11/60*2*3.1415926*$C$3</f>
+        <v>209.43950666666669</v>
+      </c>
+      <c r="E11">
+        <v>20</v>
+      </c>
+      <c r="F11">
+        <f t="shared" ref="F11:F19" si="1">$I$3/E11</f>
+        <v>1000</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" ref="I11:I19" si="2">$A$6*F11*3.1415926*2</f>
+        <v>3.1415926000000001</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" ref="J11:J19" si="3">$E$6*F11*$K$3*3.1415926*2</f>
+        <v>0.32044244520000004</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" ref="K11:K19" si="4">$C$6*F11*3.1415926*2</f>
+        <v>3.7070792680000006</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" ref="L11:L19" si="5">$E$6*F11*$K$3*3.1415926*2</f>
+        <v>0.32044244520000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0.2</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ref="B12:B19" si="6">$A$3*A12</f>
+        <v>1000</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>418.87901333333338</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="2"/>
+        <v>3.1415926000000001</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="3"/>
+        <v>0.32044244520000004</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="4"/>
+        <v>3.7070792680000006</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="5"/>
+        <v>0.32044244520000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.3</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="6"/>
+        <v>1500</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>628.31852000000003</v>
+      </c>
+      <c r="E13">
+        <v>20</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="2"/>
+        <v>3.1415926000000001</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="3"/>
+        <v>0.32044244520000004</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="4"/>
+        <v>3.7070792680000006</v>
+      </c>
+      <c r="L13" s="5">
+        <f t="shared" si="5"/>
+        <v>0.32044244520000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0.4</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="6"/>
+        <v>2000</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>837.75802666666675</v>
+      </c>
+      <c r="E14">
+        <v>30</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>666.66666666666663</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="2"/>
+        <v>2.0943950666666664</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="3"/>
+        <v>0.21362829680000003</v>
+      </c>
+      <c r="K14" s="5">
+        <f t="shared" si="4"/>
+        <v>2.4713861786666667</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="5"/>
+        <v>0.21362829680000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>0.5</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="6"/>
+        <v>2500</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>1047.1975333333332</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>666.66666666666663</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="2"/>
+        <v>2.0943950666666664</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="3"/>
+        <v>0.21362829680000003</v>
+      </c>
+      <c r="K15" s="5">
+        <f t="shared" si="4"/>
+        <v>2.4713861786666667</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="5"/>
+        <v>0.21362829680000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>0.6</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="6"/>
+        <v>3000</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>1256.6370400000001</v>
+      </c>
+      <c r="E16">
+        <v>40</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="2"/>
+        <v>1.5707963</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="3"/>
+        <v>0.16022122260000002</v>
+      </c>
+      <c r="K16" s="5">
+        <f t="shared" si="4"/>
+        <v>1.8535396340000003</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="5"/>
+        <v>0.16022122260000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>0.7</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="6"/>
+        <v>3500</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>1466.0765466666667</v>
+      </c>
+      <c r="E17">
+        <v>45</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>444.44444444444446</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="2"/>
+        <v>1.396263377777778</v>
+      </c>
+      <c r="J17" s="5">
+        <f t="shared" si="3"/>
+        <v>0.14241886453333336</v>
+      </c>
+      <c r="K17" s="5">
+        <f t="shared" si="4"/>
+        <v>1.6475907857777781</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="5"/>
+        <v>0.14241886453333336</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0.8</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="6"/>
+        <v>4000</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>1675.5160533333335</v>
+      </c>
+      <c r="E18">
+        <v>50</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="2"/>
+        <v>1.2566370400000002</v>
+      </c>
+      <c r="J18" s="5">
+        <f t="shared" si="3"/>
+        <v>0.12817697808</v>
+      </c>
+      <c r="K18" s="5">
+        <f t="shared" si="4"/>
+        <v>1.4828317072000001</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="5"/>
+        <v>0.12817697808</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="6"/>
+        <v>5000</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>2094.3950666666665</v>
+      </c>
+      <c r="E19">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>400</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="2"/>
+        <v>1.2566370400000002</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="3"/>
+        <v>0.12817697808</v>
+      </c>
+      <c r="K19" s="5">
+        <f t="shared" si="4"/>
+        <v>1.4828317072000001</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="5"/>
+        <v>0.12817697808</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65DF049C-DBC9-430D-8ECA-E64E9852A9F5}">
+  <dimension ref="A2:M22"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="16.88671875" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" customWidth="1"/>
+    <col min="10" max="10" width="25.33203125" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>5000</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <f>A3/60*2*3.1415926</f>
+        <v>523.59876666666662</v>
+      </c>
+      <c r="G3">
+        <f>A3/60*2*3.1415926*C3</f>
+        <v>2094.3950666666665</v>
+      </c>
+      <c r="I3">
+        <v>20000</v>
+      </c>
+      <c r="J3">
+        <v>4.3</v>
+      </c>
+      <c r="K3">
+        <f>1/I3</f>
+        <v>5.0000000000000002E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5.9000000000000003E-4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>0.1</v>
+      </c>
+      <c r="B10">
+        <f>$A$3*A10</f>
+        <v>500</v>
+      </c>
+      <c r="C10">
+        <f>B10/60*2*3.1415926*$C$3</f>
+        <v>209.43950666666669</v>
+      </c>
+      <c r="I10" s="6">
+        <v>9.1755000000000005E-4</v>
+      </c>
+      <c r="J10" s="6">
+        <v>9.1608999999999997E-5</v>
+      </c>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>0.1</v>
+      </c>
+      <c r="B11">
+        <f>$A$3*A11</f>
+        <v>500</v>
+      </c>
+      <c r="C11">
+        <f t="shared" ref="C11:C19" si="0">B11/60*2*3.1415926*$C$3</f>
+        <v>209.43950666666669</v>
+      </c>
+      <c r="I11" s="6">
+        <v>8.1755E-4</v>
+      </c>
+      <c r="J11" s="6">
+        <v>7.1608999999999998E-5</v>
+      </c>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>0.2</v>
+      </c>
+      <c r="B12">
+        <f t="shared" ref="B12:B19" si="1">$A$3*A12</f>
+        <v>1000</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>418.87901333333338</v>
+      </c>
+      <c r="I12" s="6">
+        <v>6.1755000000000002E-4</v>
+      </c>
+      <c r="J12" s="6">
+        <v>6.1608999999999999E-5</v>
+      </c>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>0.3</v>
+      </c>
+      <c r="B13">
+        <f t="shared" si="1"/>
+        <v>1500</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>628.31852000000003</v>
+      </c>
+      <c r="I13" s="6">
+        <v>6.1755000000000002E-4</v>
+      </c>
+      <c r="J13" s="6">
+        <v>5.1609E-5</v>
+      </c>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0.4</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="1"/>
+        <v>2000</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>837.75802666666675</v>
+      </c>
+      <c r="I14" s="6">
+        <v>6.1755000000000002E-4</v>
+      </c>
+      <c r="J14" s="6">
+        <v>5.1609E-5</v>
+      </c>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>0.5</v>
+      </c>
+      <c r="B15">
+        <f t="shared" si="1"/>
+        <v>2500</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>1047.1975333333332</v>
+      </c>
+      <c r="I15" s="6">
+        <v>5.1754999999999998E-4</v>
+      </c>
+      <c r="J15" s="7">
+        <v>7.3815823358586904E-6</v>
+      </c>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>0.6</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="1"/>
+        <v>3000</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>1256.6370400000001</v>
+      </c>
+      <c r="I16" s="8">
+        <v>9.1755000000000005E-4</v>
+      </c>
+      <c r="J16" s="7">
+        <v>7.3815823358586904E-6</v>
+      </c>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>0.7</v>
+      </c>
+      <c r="B17">
+        <f t="shared" si="1"/>
+        <v>3500</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>1466.0765466666667</v>
+      </c>
+      <c r="I17" s="8">
+        <v>9.1755000000000005E-4</v>
+      </c>
+      <c r="J17" s="7">
+        <v>7.3815823358586904E-6</v>
+      </c>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0.8</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="1"/>
+        <v>4000</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>1675.5160533333335</v>
+      </c>
+      <c r="I18" s="8">
+        <v>9.1755000000000005E-4</v>
+      </c>
+      <c r="J18" s="7">
+        <v>7.3815823358586904E-6</v>
+      </c>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>2094.3950666666665</v>
+      </c>
+      <c r="I19" s="8">
+        <v>9.1755000000000005E-4</v>
+      </c>
+      <c r="J19" s="7">
+        <v>7.3815823358586904E-6</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB951459-EFF1-4DC7-9756-A0DD0B88D824}">
+  <dimension ref="B3:G15"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>0.2</v>
+      </c>
+      <c r="E5">
+        <v>50</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <v>0.4</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="E7">
+        <v>200</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>0.8</v>
+      </c>
+      <c r="E8">
+        <v>400</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>600</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="E10">
+        <v>700</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>1.4000000000000001</v>
+      </c>
+      <c r="E11">
+        <v>750</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>1.6</v>
+      </c>
+      <c r="E12">
+        <v>800</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>800</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/PMSM_Control_01/Motor_Para.xlsx
+++ b/PMSM_Control_01/Motor_Para.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\STM32\Motor\PMSM_Control\Project\PMSM_Control_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B3FFCC-5D52-4103-904C-646A53E87A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFCAD15-4993-45E3-A443-EA25F0277185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="磁链观测器" sheetId="1" r:id="rId1"/>
     <sheet name="滑模观测器" sheetId="2" r:id="rId2"/>
-    <sheet name="DQ轴电流环" sheetId="3" r:id="rId3"/>
-    <sheet name="速度环" sheetId="4" r:id="rId4"/>
-    <sheet name="IF启动参数" sheetId="5" r:id="rId5"/>
+    <sheet name="观测器角度补偿" sheetId="7" r:id="rId3"/>
+    <sheet name="DQ轴电流环" sheetId="3" r:id="rId4"/>
+    <sheet name="速度环" sheetId="4" r:id="rId5"/>
+    <sheet name="IF启动参数" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="54">
   <si>
     <t>最大转速</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -235,6 +236,10 @@
   </si>
   <si>
     <t>IF_Start_Speed_RPM</t>
+  </si>
+  <si>
+    <t>EfFlux_Gama_Lookup_1D</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -606,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K19"/>
+  <dimension ref="A2:L19"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="17.77734375" customWidth="1"/>
@@ -614,7 +619,7 @@
     <col min="11" max="11" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -634,7 +639,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5000</v>
       </c>
@@ -657,7 +662,7 @@
         <v>5.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -685,8 +690,11 @@
       <c r="K6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.1</v>
       </c>
@@ -699,28 +707,31 @@
         <v>209.43950666666669</v>
       </c>
       <c r="D7">
-        <v>0.70699999999999996</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="E7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <f>C7*E7</f>
-        <v>104.71975333333334</v>
+        <v>209.43950666666669</v>
       </c>
       <c r="I7">
         <f>2*D7*G7</f>
-        <v>148.07373121333333</v>
+        <v>293.63418834666669</v>
       </c>
       <c r="J7">
         <f>G7*G7*$K$3</f>
-        <v>0.54831133690970901</v>
+        <v>2.1932453476388361</v>
       </c>
       <c r="K7" s="4">
         <v>100000</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.1</v>
       </c>
@@ -733,28 +744,31 @@
         <v>209.43950666666669</v>
       </c>
       <c r="D8">
-        <v>0.70699999999999996</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="E8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <f t="shared" ref="G8:G16" si="1">C8*E8</f>
-        <v>104.71975333333334</v>
+        <v>209.43950666666669</v>
       </c>
       <c r="I8">
         <f>2*D8*G8</f>
-        <v>148.07373121333333</v>
+        <v>293.63418834666669</v>
       </c>
       <c r="J8">
         <f t="shared" ref="J8:J16" si="2">G8*G8*$K$3</f>
-        <v>0.54831133690970901</v>
+        <v>2.1932453476388361</v>
       </c>
       <c r="K8" s="4">
         <v>100000</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.2</v>
       </c>
@@ -767,28 +781,31 @@
         <v>418.87901333333338</v>
       </c>
       <c r="D9">
-        <v>0.70699999999999996</v>
+        <v>0.70099999999999996</v>
       </c>
       <c r="E9">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G9">
         <f t="shared" si="1"/>
-        <v>209.43950666666669</v>
+        <v>418.87901333333338</v>
       </c>
       <c r="I9">
         <f t="shared" ref="I9:I16" si="4">2*D9*G9</f>
-        <v>296.14746242666666</v>
+        <v>587.26837669333338</v>
       </c>
       <c r="J9">
         <f t="shared" si="2"/>
-        <v>2.1932453476388361</v>
+        <v>8.7729813905553442</v>
       </c>
       <c r="K9" s="4">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.3</v>
       </c>
@@ -801,28 +818,31 @@
         <v>628.31852000000003</v>
       </c>
       <c r="D10">
-        <v>0.70699999999999996</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G10">
         <f t="shared" si="1"/>
-        <v>314.15926000000002</v>
+        <v>439.82296400000001</v>
       </c>
       <c r="I10">
         <f t="shared" si="4"/>
-        <v>444.22119364000002</v>
+        <v>879.64592800000003</v>
       </c>
       <c r="J10">
         <f t="shared" si="2"/>
-        <v>4.9348020321873802</v>
+        <v>9.6722119830872657</v>
       </c>
       <c r="K10" s="4">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.4</v>
       </c>
@@ -835,28 +855,31 @@
         <v>837.75802666666675</v>
       </c>
       <c r="D11">
-        <v>0.70699999999999996</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G11">
         <f t="shared" si="1"/>
-        <v>418.87901333333338</v>
+        <v>335.10321066666671</v>
       </c>
       <c r="I11">
         <f t="shared" si="4"/>
-        <v>592.29492485333333</v>
+        <v>1340.4128426666668</v>
       </c>
       <c r="J11">
         <f t="shared" si="2"/>
-        <v>8.7729813905553442</v>
+        <v>5.6147080899554203</v>
       </c>
       <c r="K11" s="4">
         <v>1000000</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.5</v>
       </c>
@@ -869,28 +892,31 @@
         <v>1047.1975333333332</v>
       </c>
       <c r="D12">
-        <v>0.70699999999999996</v>
+        <v>5</v>
       </c>
       <c r="E12">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G12">
         <f t="shared" si="1"/>
-        <v>523.59876666666662</v>
+        <v>104.71975333333333</v>
       </c>
       <c r="I12">
         <f t="shared" si="4"/>
-        <v>740.36865606666652</v>
+        <v>1047.1975333333332</v>
       </c>
       <c r="J12">
         <f t="shared" si="2"/>
-        <v>13.70778342274272</v>
+        <v>0.5483113369097089</v>
       </c>
       <c r="K12" s="4">
         <v>2000000</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.6</v>
       </c>
@@ -903,28 +929,31 @@
         <v>1256.6370400000001</v>
       </c>
       <c r="D13">
-        <v>0.70699999999999996</v>
+        <v>5</v>
       </c>
       <c r="E13">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G13">
         <f t="shared" si="1"/>
-        <v>628.31852000000003</v>
+        <v>125.66370400000001</v>
       </c>
       <c r="I13">
         <f t="shared" si="4"/>
-        <v>888.44238728000005</v>
+        <v>1256.6370400000001</v>
       </c>
       <c r="J13">
         <f t="shared" si="2"/>
-        <v>19.739208128749521</v>
+        <v>0.78956832514998099</v>
       </c>
       <c r="K13" s="4">
         <v>3000000</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.7</v>
       </c>
@@ -937,28 +966,31 @@
         <v>1466.0765466666667</v>
       </c>
       <c r="D14">
-        <v>0.70699999999999996</v>
+        <v>5</v>
       </c>
       <c r="E14">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G14">
         <f t="shared" si="1"/>
-        <v>733.03827333333334</v>
+        <v>146.60765466666666</v>
       </c>
       <c r="I14">
         <f t="shared" si="4"/>
-        <v>1036.5161184933334</v>
+        <v>1466.0765466666667</v>
       </c>
       <c r="J14">
         <f t="shared" si="2"/>
-        <v>26.867255508575735</v>
+        <v>1.0746902203430295</v>
       </c>
       <c r="K14" s="4">
         <v>4000000</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.8</v>
       </c>
@@ -971,28 +1003,31 @@
         <v>1675.5160533333335</v>
       </c>
       <c r="D15">
-        <v>0.70699999999999996</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G15">
         <f t="shared" si="1"/>
-        <v>837.75802666666675</v>
+        <v>167.55160533333336</v>
       </c>
       <c r="I15">
         <f t="shared" si="4"/>
-        <v>1184.5898497066667</v>
+        <v>1675.5160533333335</v>
       </c>
       <c r="J15">
         <f t="shared" si="2"/>
-        <v>35.091925562221377</v>
+        <v>1.4036770224888551</v>
       </c>
       <c r="K15" s="4">
         <v>5000000</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1005,28 +1040,31 @@
         <v>2094.3950666666665</v>
       </c>
       <c r="D16">
-        <v>0.70699999999999996</v>
+        <v>5</v>
       </c>
       <c r="E16">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="G16">
         <f t="shared" si="1"/>
-        <v>1047.1975333333332</v>
+        <v>209.43950666666666</v>
       </c>
       <c r="I16">
         <f t="shared" si="4"/>
-        <v>1480.737312133333</v>
+        <v>2094.3950666666665</v>
       </c>
       <c r="J16">
         <f t="shared" si="2"/>
-        <v>54.83113369097088</v>
+        <v>2.1932453476388356</v>
       </c>
       <c r="K16" s="4">
         <v>5000000</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -1042,8 +1080,11 @@
       <c r="K18" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1057,6 +1098,9 @@
         <v>17</v>
       </c>
       <c r="K19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1581,6 +1625,16 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4DC339-20AE-4EE9-9B61-D2ADC615686C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3ACED9-E871-45D1-8053-80BA01B87099}">
   <dimension ref="A2:L22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -1705,27 +1759,27 @@
         <v>209.43950666666669</v>
       </c>
       <c r="E10">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F10">
         <f>$I$3/E10</f>
-        <v>1000</v>
+        <v>666.66666666666663</v>
       </c>
       <c r="I10" s="5">
         <f>$A$6*F10*3.1415926*2</f>
-        <v>3.1415926000000001</v>
+        <v>2.0943950666666664</v>
       </c>
       <c r="J10" s="5">
         <f>$E$6*F10*$K$3*3.1415926*2</f>
-        <v>0.32044244520000004</v>
+        <v>0.21362829680000003</v>
       </c>
       <c r="K10" s="5">
         <f>$C$6*F10*3.1415926*2</f>
-        <v>3.7070792680000006</v>
+        <v>2.4713861786666667</v>
       </c>
       <c r="L10" s="5">
         <f>$E$6*F10*$K$3*3.1415926*2</f>
-        <v>0.32044244520000004</v>
+        <v>0.21362829680000003</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -1741,27 +1795,27 @@
         <v>209.43950666666669</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <f t="shared" ref="F11:F19" si="1">$I$3/E11</f>
-        <v>1000</v>
+        <v>666.66666666666663</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11:I19" si="2">$A$6*F11*3.1415926*2</f>
-        <v>3.1415926000000001</v>
+        <v>2.0943950666666664</v>
       </c>
       <c r="J11" s="5">
         <f t="shared" ref="J11:J19" si="3">$E$6*F11*$K$3*3.1415926*2</f>
-        <v>0.32044244520000004</v>
+        <v>0.21362829680000003</v>
       </c>
       <c r="K11" s="5">
         <f t="shared" ref="K11:K19" si="4">$C$6*F11*3.1415926*2</f>
-        <v>3.7070792680000006</v>
+        <v>2.4713861786666667</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" ref="L11:L19" si="5">$E$6*F11*$K$3*3.1415926*2</f>
-        <v>0.32044244520000004</v>
+        <v>0.21362829680000003</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1777,27 +1831,27 @@
         <v>418.87901333333338</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F12">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>666.66666666666663</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="2"/>
-        <v>3.1415926000000001</v>
+        <v>2.0943950666666664</v>
       </c>
       <c r="J12" s="5">
         <f t="shared" si="3"/>
-        <v>0.32044244520000004</v>
+        <v>0.21362829680000003</v>
       </c>
       <c r="K12" s="5">
         <f t="shared" si="4"/>
-        <v>3.7070792680000006</v>
+        <v>2.4713861786666667</v>
       </c>
       <c r="L12" s="5">
         <f t="shared" si="5"/>
-        <v>0.32044244520000004</v>
+        <v>0.21362829680000003</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1813,27 +1867,27 @@
         <v>628.31852000000003</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F13">
         <f t="shared" si="1"/>
-        <v>1000</v>
+        <v>666.66666666666663</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="2"/>
-        <v>3.1415926000000001</v>
+        <v>2.0943950666666664</v>
       </c>
       <c r="J13" s="5">
         <f t="shared" si="3"/>
-        <v>0.32044244520000004</v>
+        <v>0.21362829680000003</v>
       </c>
       <c r="K13" s="5">
         <f t="shared" si="4"/>
-        <v>3.7070792680000006</v>
+        <v>2.4713861786666667</v>
       </c>
       <c r="L13" s="5">
         <f t="shared" si="5"/>
-        <v>0.32044244520000004</v>
+        <v>0.21362829680000003</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2099,7 +2153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65DF049C-DBC9-430D-8ECA-E64E9852A9F5}">
   <dimension ref="A2:M22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
@@ -2448,7 +2502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB951459-EFF1-4DC7-9756-A0DD0B88D824}">
   <dimension ref="B3:G15"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>

--- a/PMSM_Control_01/Motor_Para.xlsx
+++ b/PMSM_Control_01/Motor_Para.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\STM32\Motor\PMSM_Control\Project\PMSM_Control_01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFCAD15-4993-45E3-A443-EA25F0277185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D17A7384-3BB2-4A70-B7B7-9C549631EAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="磁链观测器" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="59">
   <si>
     <t>最大转速</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -240,6 +240,25 @@
   <si>
     <t>EfFlux_Gama_Lookup_1D</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相电流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大相电流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NonFlux_Lookup_Is_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EFFlux_Angle_Comp_table_2D</t>
   </si>
 </sst>
 </file>
@@ -611,7 +630,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:L19"/>
+  <dimension ref="A2:N19"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="17.77734375" customWidth="1"/>
@@ -619,7 +638,7 @@
     <col min="11" max="11" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -638,8 +657,11 @@
       <c r="K2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5000</v>
       </c>
@@ -661,8 +683,11 @@
         <f>1/I3</f>
         <v>5.0000000000000002E-5</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -693,8 +718,11 @@
       <c r="L6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>0.1</v>
       </c>
@@ -730,8 +758,12 @@
       <c r="L7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N7">
+        <f>$N$3*A7</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>0.1</v>
       </c>
@@ -767,13 +799,17 @@
       <c r="L8">
         <v>200</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N8">
+        <f t="shared" ref="N8:N16" si="3">$N$3*A8</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>0.2</v>
       </c>
       <c r="B9">
-        <f t="shared" ref="B9:B16" si="3">$A$3*A9</f>
+        <f t="shared" ref="B9:B16" si="4">$A$3*A9</f>
         <v>1000</v>
       </c>
       <c r="C9">
@@ -791,7 +827,7 @@
         <v>418.87901333333338</v>
       </c>
       <c r="I9">
-        <f t="shared" ref="I9:I16" si="4">2*D9*G9</f>
+        <f t="shared" ref="I9:I16" si="5">2*D9*G9</f>
         <v>587.26837669333338</v>
       </c>
       <c r="J9">
@@ -804,13 +840,17 @@
       <c r="L9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>0.3</v>
       </c>
       <c r="B10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1500</v>
       </c>
       <c r="C10">
@@ -828,7 +868,7 @@
         <v>439.82296400000001</v>
       </c>
       <c r="I10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>879.64592800000003</v>
       </c>
       <c r="J10">
@@ -841,13 +881,17 @@
       <c r="L10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>0.4</v>
       </c>
       <c r="B11">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2000</v>
       </c>
       <c r="C11">
@@ -865,7 +909,7 @@
         <v>335.10321066666671</v>
       </c>
       <c r="I11">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1340.4128426666668</v>
       </c>
       <c r="J11">
@@ -878,13 +922,17 @@
       <c r="L11">
         <v>200</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N11">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>0.5</v>
       </c>
       <c r="B12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2500</v>
       </c>
       <c r="C12">
@@ -902,7 +950,7 @@
         <v>104.71975333333333</v>
       </c>
       <c r="I12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1047.1975333333332</v>
       </c>
       <c r="J12">
@@ -915,13 +963,17 @@
       <c r="L12">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N12">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>0.6</v>
       </c>
       <c r="B13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3000</v>
       </c>
       <c r="C13">
@@ -939,7 +991,7 @@
         <v>125.66370400000001</v>
       </c>
       <c r="I13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1256.6370400000001</v>
       </c>
       <c r="J13">
@@ -952,13 +1004,17 @@
       <c r="L13">
         <v>200</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>0.7</v>
       </c>
       <c r="B14">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3500</v>
       </c>
       <c r="C14">
@@ -976,7 +1032,7 @@
         <v>146.60765466666666</v>
       </c>
       <c r="I14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1466.0765466666667</v>
       </c>
       <c r="J14">
@@ -989,13 +1045,17 @@
       <c r="L14">
         <v>200</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N14">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>0.8</v>
       </c>
       <c r="B15">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4000</v>
       </c>
       <c r="C15">
@@ -1013,7 +1073,7 @@
         <v>167.55160533333336</v>
       </c>
       <c r="I15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1675.5160533333335</v>
       </c>
       <c r="J15">
@@ -1026,13 +1086,17 @@
       <c r="L15">
         <v>200</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="B16">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5000</v>
       </c>
       <c r="C16">
@@ -1050,7 +1114,7 @@
         <v>209.43950666666666</v>
       </c>
       <c r="I16">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2094.3950666666665</v>
       </c>
       <c r="J16">
@@ -1063,8 +1127,12 @@
       <c r="L16">
         <v>200</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N16">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -1083,8 +1151,11 @@
       <c r="L18" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N18" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1101,6 +1172,9 @@
         <v>17</v>
       </c>
       <c r="L19" t="s">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1626,9 +1700,402 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4DC339-20AE-4EE9-9B61-D2ADC615686C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>18</v>
+      </c>
+      <c r="I3">
+        <v>21</v>
+      </c>
+      <c r="J3">
+        <v>24</v>
+      </c>
+      <c r="K3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>500</v>
+      </c>
+      <c r="B4">
+        <v>-0.05</v>
+      </c>
+      <c r="C4">
+        <v>-0.05</v>
+      </c>
+      <c r="D4">
+        <v>-0.05</v>
+      </c>
+      <c r="E4">
+        <v>-0.05</v>
+      </c>
+      <c r="F4">
+        <v>-0.05</v>
+      </c>
+      <c r="G4">
+        <v>-0.05</v>
+      </c>
+      <c r="H4">
+        <v>-0.05</v>
+      </c>
+      <c r="I4">
+        <v>-0.05</v>
+      </c>
+      <c r="J4">
+        <v>-0.05</v>
+      </c>
+      <c r="K4">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>500</v>
+      </c>
+      <c r="B5">
+        <v>-0.05</v>
+      </c>
+      <c r="C5">
+        <v>-0.05</v>
+      </c>
+      <c r="D5">
+        <v>-0.05</v>
+      </c>
+      <c r="E5">
+        <v>-0.05</v>
+      </c>
+      <c r="F5">
+        <v>-0.05</v>
+      </c>
+      <c r="G5">
+        <v>-0.05</v>
+      </c>
+      <c r="H5">
+        <v>-0.05</v>
+      </c>
+      <c r="I5">
+        <v>-0.05</v>
+      </c>
+      <c r="J5">
+        <v>-0.05</v>
+      </c>
+      <c r="K5">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1000</v>
+      </c>
+      <c r="B6">
+        <v>-0.05</v>
+      </c>
+      <c r="C6">
+        <v>-0.05</v>
+      </c>
+      <c r="D6">
+        <v>-0.05</v>
+      </c>
+      <c r="E6">
+        <v>-0.05</v>
+      </c>
+      <c r="F6">
+        <v>-0.05</v>
+      </c>
+      <c r="G6">
+        <v>-0.05</v>
+      </c>
+      <c r="H6">
+        <v>-0.05</v>
+      </c>
+      <c r="I6">
+        <v>-0.05</v>
+      </c>
+      <c r="J6">
+        <v>-0.05</v>
+      </c>
+      <c r="K6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1500</v>
+      </c>
+      <c r="B7">
+        <v>-0.05</v>
+      </c>
+      <c r="C7">
+        <v>-0.05</v>
+      </c>
+      <c r="D7">
+        <v>-0.05</v>
+      </c>
+      <c r="E7">
+        <v>-0.05</v>
+      </c>
+      <c r="F7">
+        <v>-0.05</v>
+      </c>
+      <c r="G7">
+        <v>-0.05</v>
+      </c>
+      <c r="H7">
+        <v>-0.05</v>
+      </c>
+      <c r="I7">
+        <v>-0.05</v>
+      </c>
+      <c r="J7">
+        <v>-0.05</v>
+      </c>
+      <c r="K7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2000</v>
+      </c>
+      <c r="B8">
+        <v>-0.05</v>
+      </c>
+      <c r="C8">
+        <v>-0.05</v>
+      </c>
+      <c r="D8">
+        <v>-0.05</v>
+      </c>
+      <c r="E8">
+        <v>-0.05</v>
+      </c>
+      <c r="F8">
+        <v>-0.05</v>
+      </c>
+      <c r="G8">
+        <v>-0.05</v>
+      </c>
+      <c r="H8">
+        <v>-0.05</v>
+      </c>
+      <c r="I8">
+        <v>-0.05</v>
+      </c>
+      <c r="J8">
+        <v>-0.05</v>
+      </c>
+      <c r="K8">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2500</v>
+      </c>
+      <c r="B9">
+        <v>-0.05</v>
+      </c>
+      <c r="C9">
+        <v>-0.05</v>
+      </c>
+      <c r="D9">
+        <v>-0.05</v>
+      </c>
+      <c r="E9">
+        <v>-0.05</v>
+      </c>
+      <c r="F9">
+        <v>-0.05</v>
+      </c>
+      <c r="G9">
+        <v>-0.05</v>
+      </c>
+      <c r="H9">
+        <v>-0.05</v>
+      </c>
+      <c r="I9">
+        <v>-0.05</v>
+      </c>
+      <c r="J9">
+        <v>-0.05</v>
+      </c>
+      <c r="K9">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>3000</v>
+      </c>
+      <c r="B10">
+        <v>-0.05</v>
+      </c>
+      <c r="C10">
+        <v>-0.05</v>
+      </c>
+      <c r="D10">
+        <v>-0.05</v>
+      </c>
+      <c r="E10">
+        <v>-0.05</v>
+      </c>
+      <c r="F10">
+        <v>-0.05</v>
+      </c>
+      <c r="G10">
+        <v>-0.05</v>
+      </c>
+      <c r="H10">
+        <v>-0.05</v>
+      </c>
+      <c r="I10">
+        <v>-0.05</v>
+      </c>
+      <c r="J10">
+        <v>-0.05</v>
+      </c>
+      <c r="K10">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3500</v>
+      </c>
+      <c r="B11">
+        <v>-0.05</v>
+      </c>
+      <c r="C11">
+        <v>-0.05</v>
+      </c>
+      <c r="D11">
+        <v>-0.05</v>
+      </c>
+      <c r="E11">
+        <v>-0.05</v>
+      </c>
+      <c r="F11">
+        <v>-0.05</v>
+      </c>
+      <c r="G11">
+        <v>-0.05</v>
+      </c>
+      <c r="H11">
+        <v>-0.05</v>
+      </c>
+      <c r="I11">
+        <v>-0.05</v>
+      </c>
+      <c r="J11">
+        <v>-0.05</v>
+      </c>
+      <c r="K11">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>4000</v>
+      </c>
+      <c r="B12">
+        <v>-0.05</v>
+      </c>
+      <c r="C12">
+        <v>-0.05</v>
+      </c>
+      <c r="D12">
+        <v>-0.05</v>
+      </c>
+      <c r="E12">
+        <v>-0.05</v>
+      </c>
+      <c r="F12">
+        <v>-0.05</v>
+      </c>
+      <c r="G12">
+        <v>-0.05</v>
+      </c>
+      <c r="H12">
+        <v>-0.05</v>
+      </c>
+      <c r="I12">
+        <v>-0.05</v>
+      </c>
+      <c r="J12">
+        <v>-0.05</v>
+      </c>
+      <c r="K12">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>5000</v>
+      </c>
+      <c r="B13">
+        <v>-0.05</v>
+      </c>
+      <c r="C13">
+        <v>-0.05</v>
+      </c>
+      <c r="D13">
+        <v>-0.05</v>
+      </c>
+      <c r="E13">
+        <v>-0.05</v>
+      </c>
+      <c r="F13">
+        <v>-0.05</v>
+      </c>
+      <c r="G13">
+        <v>-0.05</v>
+      </c>
+      <c r="H13">
+        <v>-0.05</v>
+      </c>
+      <c r="I13">
+        <v>-0.05</v>
+      </c>
+      <c r="J13">
+        <v>-0.05</v>
+      </c>
+      <c r="K13">
+        <v>-0.05</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2504,7 +2971,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB951459-EFF1-4DC7-9756-A0DD0B88D824}">
-  <dimension ref="B3:G15"/>
+  <dimension ref="B3:I22"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
@@ -2656,6 +3123,11 @@
         <v>17</v>
       </c>
     </row>
+    <row r="22" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I22" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
